--- a/Chapters/Chapter 2 - Color and Weave Effects/Color & Weave Effects.xlsx
+++ b/Chapters/Chapter 2 - Color and Weave Effects/Color & Weave Effects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fabric Structure and Design (FSD)\Chapters\Chapter 2 - Color and Weave Effects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5216B5F-DC44-4581-91A9-D1C4ED01A8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4BB727-4721-4447-8B94-2FBD6CF51C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="876" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5014" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5527" uniqueCount="2">
   <si>
     <t>#</t>
   </si>
@@ -70,7 +70,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,6 +146,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -408,6 +414,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1067,7 +1079,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F041D7F-7414-4FB3-A7F1-DF93A3DEC1C2}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="D5:FW82"/>
+  <dimension ref="D5:FW134"/>
   <sheetFormatPr defaultColWidth="3.5546875" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="3.5546875" style="1"/>
@@ -6325,74 +6337,6 @@
       <c r="AR31" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="BA31" s="4"/>
-      <c r="BB31" s="1">
-        <v>16</v>
-      </c>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="5"/>
-      <c r="BE31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG31" s="5"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK31" s="5"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO31" s="5"/>
-      <c r="BP31" s="5"/>
-      <c r="BQ31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS31" s="5"/>
-      <c r="BT31" s="5"/>
-      <c r="BU31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW31" s="5"/>
-      <c r="BX31" s="5"/>
-      <c r="BY31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA31" s="5"/>
-      <c r="CB31" s="5"/>
-      <c r="CC31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE31" s="5"/>
-      <c r="CF31" s="5"/>
-      <c r="CG31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH31" s="6" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="32" spans="4:122" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F32" s="4"/>
@@ -6467,75 +6411,6 @@
         <v>1</v>
       </c>
       <c r="AR32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA32" s="4"/>
-      <c r="BB32" s="1">
-        <f>BB31-1</f>
-        <v>15</v>
-      </c>
-      <c r="BC32" s="5"/>
-      <c r="BD32" s="5"/>
-      <c r="BE32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG32" s="5"/>
-      <c r="BH32" s="5"/>
-      <c r="BI32" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ32" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK32" s="5"/>
-      <c r="BL32" s="5"/>
-      <c r="BM32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO32" s="5"/>
-      <c r="BP32" s="5"/>
-      <c r="BQ32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS32" s="5"/>
-      <c r="BT32" s="5"/>
-      <c r="BU32" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV32" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW32" s="5"/>
-      <c r="BX32" s="5"/>
-      <c r="BY32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA32" s="5"/>
-      <c r="CB32" s="5"/>
-      <c r="CC32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE32" s="5"/>
-      <c r="CF32" s="5"/>
-      <c r="CG32" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH32" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6614,75 +6489,6 @@
       </c>
       <c r="AQ33" s="5"/>
       <c r="AR33" s="5"/>
-      <c r="BA33" s="7"/>
-      <c r="BB33" s="1">
-        <f t="shared" ref="BB33:BB46" si="16">BB32-1</f>
-        <v>14</v>
-      </c>
-      <c r="BC33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE33" s="6"/>
-      <c r="BF33" s="6"/>
-      <c r="BG33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI33" s="6"/>
-      <c r="BJ33" s="6"/>
-      <c r="BK33" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL33" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM33" s="6"/>
-      <c r="BN33" s="6"/>
-      <c r="BO33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ33" s="6"/>
-      <c r="BR33" s="6"/>
-      <c r="BS33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU33" s="6"/>
-      <c r="BV33" s="6"/>
-      <c r="BW33" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX33" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY33" s="6"/>
-      <c r="BZ33" s="6"/>
-      <c r="CA33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC33" s="6"/>
-      <c r="CD33" s="6"/>
-      <c r="CE33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG33" s="6"/>
-      <c r="CH33" s="6"/>
     </row>
     <row r="34" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F34" s="7"/>
@@ -6759,75 +6565,6 @@
       </c>
       <c r="AQ34" s="5"/>
       <c r="AR34" s="5"/>
-      <c r="BA34" s="7"/>
-      <c r="BB34" s="1">
-        <f t="shared" si="16"/>
-        <v>13</v>
-      </c>
-      <c r="BC34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE34" s="6"/>
-      <c r="BF34" s="6"/>
-      <c r="BG34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI34" s="6"/>
-      <c r="BJ34" s="6"/>
-      <c r="BK34" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL34" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM34" s="6"/>
-      <c r="BN34" s="6"/>
-      <c r="BO34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ34" s="6"/>
-      <c r="BR34" s="6"/>
-      <c r="BS34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU34" s="6"/>
-      <c r="BV34" s="6"/>
-      <c r="BW34" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX34" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY34" s="6"/>
-      <c r="BZ34" s="6"/>
-      <c r="CA34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC34" s="6"/>
-      <c r="CD34" s="6"/>
-      <c r="CE34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG34" s="6"/>
-      <c r="CH34" s="6"/>
     </row>
     <row r="35" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F35" s="4"/>
@@ -6904,75 +6641,6 @@
       <c r="AR35" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="BA35" s="4"/>
-      <c r="BB35" s="1">
-        <f t="shared" si="16"/>
-        <v>12</v>
-      </c>
-      <c r="BC35" s="5"/>
-      <c r="BD35" s="5"/>
-      <c r="BE35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG35" s="5"/>
-      <c r="BH35" s="5"/>
-      <c r="BI35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK35" s="5"/>
-      <c r="BL35" s="5"/>
-      <c r="BM35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO35" s="5"/>
-      <c r="BP35" s="5"/>
-      <c r="BQ35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS35" s="5"/>
-      <c r="BT35" s="5"/>
-      <c r="BU35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW35" s="5"/>
-      <c r="BX35" s="5"/>
-      <c r="BY35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA35" s="5"/>
-      <c r="CB35" s="5"/>
-      <c r="CC35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE35" s="5"/>
-      <c r="CF35" s="5"/>
-      <c r="CG35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH35" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="CN35" s="5"/>
       <c r="CO35" s="5"/>
       <c r="CP35" s="5" t="s">
@@ -7215,75 +6883,6 @@
         <v>1</v>
       </c>
       <c r="AR36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA36" s="4"/>
-      <c r="BB36" s="1">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="BC36" s="5"/>
-      <c r="BD36" s="5"/>
-      <c r="BE36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG36" s="5"/>
-      <c r="BH36" s="5"/>
-      <c r="BI36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK36" s="5"/>
-      <c r="BL36" s="5"/>
-      <c r="BM36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO36" s="5"/>
-      <c r="BP36" s="5"/>
-      <c r="BQ36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS36" s="5"/>
-      <c r="BT36" s="5"/>
-      <c r="BU36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW36" s="5"/>
-      <c r="BX36" s="5"/>
-      <c r="BY36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA36" s="5"/>
-      <c r="CB36" s="5"/>
-      <c r="CC36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE36" s="5"/>
-      <c r="CF36" s="5"/>
-      <c r="CG36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH36" s="6" t="s">
         <v>1</v>
       </c>
       <c r="CN36" s="5"/>
@@ -7530,75 +7129,6 @@
       </c>
       <c r="AQ37" s="5"/>
       <c r="AR37" s="5"/>
-      <c r="BA37" s="7"/>
-      <c r="BB37" s="1">
-        <f t="shared" si="16"/>
-        <v>10</v>
-      </c>
-      <c r="BC37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE37" s="6"/>
-      <c r="BF37" s="6"/>
-      <c r="BG37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI37" s="6"/>
-      <c r="BJ37" s="6"/>
-      <c r="BK37" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL37" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM37" s="6"/>
-      <c r="BN37" s="6"/>
-      <c r="BO37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ37" s="6"/>
-      <c r="BR37" s="6"/>
-      <c r="BS37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU37" s="6"/>
-      <c r="BV37" s="6"/>
-      <c r="BW37" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX37" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY37" s="6"/>
-      <c r="BZ37" s="6"/>
-      <c r="CA37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC37" s="6"/>
-      <c r="CD37" s="6"/>
-      <c r="CE37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG37" s="6"/>
-      <c r="CH37" s="6"/>
       <c r="CN37" s="6" t="s">
         <v>1</v>
       </c>
@@ -7843,75 +7373,6 @@
       </c>
       <c r="AQ38" s="6"/>
       <c r="AR38" s="6"/>
-      <c r="BA38" s="7"/>
-      <c r="BB38" s="1">
-        <f t="shared" si="16"/>
-        <v>9</v>
-      </c>
-      <c r="BC38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE38" s="6"/>
-      <c r="BF38" s="6"/>
-      <c r="BG38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI38" s="6"/>
-      <c r="BJ38" s="6"/>
-      <c r="BK38" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL38" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM38" s="6"/>
-      <c r="BN38" s="6"/>
-      <c r="BO38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ38" s="6"/>
-      <c r="BR38" s="6"/>
-      <c r="BS38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU38" s="6"/>
-      <c r="BV38" s="6"/>
-      <c r="BW38" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX38" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY38" s="6"/>
-      <c r="BZ38" s="6"/>
-      <c r="CA38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC38" s="6"/>
-      <c r="CD38" s="6"/>
-      <c r="CE38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG38" s="6"/>
-      <c r="CH38" s="6"/>
       <c r="CN38" s="6" t="s">
         <v>1</v>
       </c>
@@ -8156,75 +7617,6 @@
       <c r="AR39" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="BA39" s="4"/>
-      <c r="BB39" s="1">
-        <f t="shared" si="16"/>
-        <v>8</v>
-      </c>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="5"/>
-      <c r="BE39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG39" s="5"/>
-      <c r="BH39" s="5"/>
-      <c r="BI39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK39" s="5"/>
-      <c r="BL39" s="5"/>
-      <c r="BM39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO39" s="5"/>
-      <c r="BP39" s="5"/>
-      <c r="BQ39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS39" s="5"/>
-      <c r="BT39" s="5"/>
-      <c r="BU39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW39" s="5"/>
-      <c r="BX39" s="5"/>
-      <c r="BY39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA39" s="5"/>
-      <c r="CB39" s="5"/>
-      <c r="CC39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE39" s="5"/>
-      <c r="CF39" s="5"/>
-      <c r="CG39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH39" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="CN39" s="5"/>
       <c r="CO39" s="5"/>
       <c r="CP39" s="5" t="s">
@@ -8467,75 +7859,6 @@
         <v>1</v>
       </c>
       <c r="AR40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA40" s="4"/>
-      <c r="BB40" s="1">
-        <f t="shared" si="16"/>
-        <v>7</v>
-      </c>
-      <c r="BC40" s="5"/>
-      <c r="BD40" s="5"/>
-      <c r="BE40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG40" s="5"/>
-      <c r="BH40" s="5"/>
-      <c r="BI40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK40" s="5"/>
-      <c r="BL40" s="5"/>
-      <c r="BM40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO40" s="5"/>
-      <c r="BP40" s="5"/>
-      <c r="BQ40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS40" s="5"/>
-      <c r="BT40" s="5"/>
-      <c r="BU40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW40" s="5"/>
-      <c r="BX40" s="5"/>
-      <c r="BY40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA40" s="5"/>
-      <c r="CB40" s="5"/>
-      <c r="CC40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE40" s="5"/>
-      <c r="CF40" s="5"/>
-      <c r="CG40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH40" s="6" t="s">
         <v>1</v>
       </c>
       <c r="CN40" s="5"/>
@@ -8782,75 +8105,6 @@
       </c>
       <c r="AQ41" s="6"/>
       <c r="AR41" s="6"/>
-      <c r="BA41" s="7"/>
-      <c r="BB41" s="1">
-        <f t="shared" si="16"/>
-        <v>6</v>
-      </c>
-      <c r="BC41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE41" s="6"/>
-      <c r="BF41" s="6"/>
-      <c r="BG41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI41" s="6"/>
-      <c r="BJ41" s="6"/>
-      <c r="BK41" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL41" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM41" s="6"/>
-      <c r="BN41" s="6"/>
-      <c r="BO41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ41" s="6"/>
-      <c r="BR41" s="6"/>
-      <c r="BS41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU41" s="6"/>
-      <c r="BV41" s="6"/>
-      <c r="BW41" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX41" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY41" s="6"/>
-      <c r="BZ41" s="6"/>
-      <c r="CA41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC41" s="6"/>
-      <c r="CD41" s="6"/>
-      <c r="CE41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG41" s="6"/>
-      <c r="CH41" s="6"/>
       <c r="CN41" s="6" t="s">
         <v>1</v>
       </c>
@@ -9095,75 +8349,6 @@
       </c>
       <c r="AQ42" s="6"/>
       <c r="AR42" s="6"/>
-      <c r="BA42" s="7"/>
-      <c r="BB42" s="1">
-        <f t="shared" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="BC42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE42" s="6"/>
-      <c r="BF42" s="6"/>
-      <c r="BG42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI42" s="6"/>
-      <c r="BJ42" s="6"/>
-      <c r="BK42" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL42" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM42" s="6"/>
-      <c r="BN42" s="6"/>
-      <c r="BO42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ42" s="6"/>
-      <c r="BR42" s="6"/>
-      <c r="BS42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU42" s="6"/>
-      <c r="BV42" s="6"/>
-      <c r="BW42" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX42" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY42" s="6"/>
-      <c r="BZ42" s="6"/>
-      <c r="CA42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC42" s="6"/>
-      <c r="CD42" s="6"/>
-      <c r="CE42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG42" s="6"/>
-      <c r="CH42" s="6"/>
       <c r="CN42" s="6" t="s">
         <v>1</v>
       </c>
@@ -9408,75 +8593,6 @@
       <c r="AR43" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="BA43" s="4"/>
-      <c r="BB43" s="1">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="BC43" s="5"/>
-      <c r="BD43" s="5"/>
-      <c r="BE43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG43" s="5"/>
-      <c r="BH43" s="5"/>
-      <c r="BI43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK43" s="5"/>
-      <c r="BL43" s="5"/>
-      <c r="BM43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO43" s="5"/>
-      <c r="BP43" s="5"/>
-      <c r="BQ43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS43" s="5"/>
-      <c r="BT43" s="5"/>
-      <c r="BU43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW43" s="5"/>
-      <c r="BX43" s="5"/>
-      <c r="BY43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA43" s="5"/>
-      <c r="CB43" s="5"/>
-      <c r="CC43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE43" s="5"/>
-      <c r="CF43" s="5"/>
-      <c r="CG43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH43" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="CN43" s="5"/>
       <c r="CO43" s="5"/>
       <c r="CP43" s="5" t="s">
@@ -9719,75 +8835,6 @@
         <v>1</v>
       </c>
       <c r="AR44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA44" s="4"/>
-      <c r="BB44" s="1">
-        <f t="shared" si="16"/>
-        <v>3</v>
-      </c>
-      <c r="BC44" s="5"/>
-      <c r="BD44" s="5"/>
-      <c r="BE44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG44" s="5"/>
-      <c r="BH44" s="5"/>
-      <c r="BI44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK44" s="5"/>
-      <c r="BL44" s="5"/>
-      <c r="BM44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO44" s="5"/>
-      <c r="BP44" s="5"/>
-      <c r="BQ44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS44" s="5"/>
-      <c r="BT44" s="5"/>
-      <c r="BU44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW44" s="5"/>
-      <c r="BX44" s="5"/>
-      <c r="BY44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BZ44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CA44" s="5"/>
-      <c r="CB44" s="5"/>
-      <c r="CC44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CD44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="CE44" s="5"/>
-      <c r="CF44" s="5"/>
-      <c r="CG44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CH44" s="6" t="s">
         <v>1</v>
       </c>
       <c r="CN44" s="5"/>
@@ -10034,75 +9081,6 @@
       </c>
       <c r="AQ45" s="5"/>
       <c r="AR45" s="5"/>
-      <c r="BA45" s="7"/>
-      <c r="BB45" s="1">
-        <f t="shared" si="16"/>
-        <v>2</v>
-      </c>
-      <c r="BC45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE45" s="6"/>
-      <c r="BF45" s="6"/>
-      <c r="BG45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI45" s="6"/>
-      <c r="BJ45" s="6"/>
-      <c r="BK45" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL45" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM45" s="6"/>
-      <c r="BN45" s="6"/>
-      <c r="BO45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ45" s="6"/>
-      <c r="BR45" s="6"/>
-      <c r="BS45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU45" s="6"/>
-      <c r="BV45" s="6"/>
-      <c r="BW45" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX45" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY45" s="6"/>
-      <c r="BZ45" s="6"/>
-      <c r="CA45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC45" s="6"/>
-      <c r="CD45" s="6"/>
-      <c r="CE45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG45" s="6"/>
-      <c r="CH45" s="6"/>
       <c r="CN45" s="6" t="s">
         <v>1</v>
       </c>
@@ -10345,75 +9323,6 @@
       </c>
       <c r="AQ46" s="5"/>
       <c r="AR46" s="5"/>
-      <c r="BA46" s="7"/>
-      <c r="BB46" s="1">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="BC46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE46" s="6"/>
-      <c r="BF46" s="6"/>
-      <c r="BG46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI46" s="6"/>
-      <c r="BJ46" s="6"/>
-      <c r="BK46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM46" s="6"/>
-      <c r="BN46" s="6"/>
-      <c r="BO46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ46" s="6"/>
-      <c r="BR46" s="6"/>
-      <c r="BS46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU46" s="6"/>
-      <c r="BV46" s="6"/>
-      <c r="BW46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BY46" s="6"/>
-      <c r="BZ46" s="6"/>
-      <c r="CA46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CB46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CC46" s="6"/>
-      <c r="CD46" s="6"/>
-      <c r="CE46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="CG46" s="6"/>
-      <c r="CH46" s="6"/>
       <c r="CN46" s="6" t="s">
         <v>1</v>
       </c>
@@ -10655,136 +9564,6 @@
       </c>
       <c r="AR47" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="BB47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC47" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD47" s="1">
-        <f>BC47+1</f>
-        <v>2</v>
-      </c>
-      <c r="BE47" s="1">
-        <f t="shared" ref="BE47" si="17">BD47+1</f>
-        <v>3</v>
-      </c>
-      <c r="BF47" s="1">
-        <f t="shared" ref="BF47" si="18">BE47+1</f>
-        <v>4</v>
-      </c>
-      <c r="BG47" s="1">
-        <f t="shared" ref="BG47" si="19">BF47+1</f>
-        <v>5</v>
-      </c>
-      <c r="BH47" s="1">
-        <f t="shared" ref="BH47" si="20">BG47+1</f>
-        <v>6</v>
-      </c>
-      <c r="BI47" s="1">
-        <f t="shared" ref="BI47" si="21">BH47+1</f>
-        <v>7</v>
-      </c>
-      <c r="BJ47" s="1">
-        <f t="shared" ref="BJ47" si="22">BI47+1</f>
-        <v>8</v>
-      </c>
-      <c r="BK47" s="1">
-        <f t="shared" ref="BK47" si="23">BJ47+1</f>
-        <v>9</v>
-      </c>
-      <c r="BL47" s="1">
-        <f t="shared" ref="BL47" si="24">BK47+1</f>
-        <v>10</v>
-      </c>
-      <c r="BM47" s="1">
-        <f t="shared" ref="BM47" si="25">BL47+1</f>
-        <v>11</v>
-      </c>
-      <c r="BN47" s="1">
-        <f t="shared" ref="BN47" si="26">BM47+1</f>
-        <v>12</v>
-      </c>
-      <c r="BO47" s="1">
-        <f t="shared" ref="BO47" si="27">BN47+1</f>
-        <v>13</v>
-      </c>
-      <c r="BP47" s="1">
-        <f t="shared" ref="BP47" si="28">BO47+1</f>
-        <v>14</v>
-      </c>
-      <c r="BQ47" s="1">
-        <f t="shared" ref="BQ47" si="29">BP47+1</f>
-        <v>15</v>
-      </c>
-      <c r="BR47" s="1">
-        <f t="shared" ref="BR47" si="30">BQ47+1</f>
-        <v>16</v>
-      </c>
-      <c r="BS47" s="1">
-        <f t="shared" ref="BS47" si="31">BR47+1</f>
-        <v>17</v>
-      </c>
-      <c r="BT47" s="1">
-        <f t="shared" ref="BT47" si="32">BS47+1</f>
-        <v>18</v>
-      </c>
-      <c r="BU47" s="1">
-        <f t="shared" ref="BU47" si="33">BT47+1</f>
-        <v>19</v>
-      </c>
-      <c r="BV47" s="1">
-        <f t="shared" ref="BV47" si="34">BU47+1</f>
-        <v>20</v>
-      </c>
-      <c r="BW47" s="1">
-        <f t="shared" ref="BW47" si="35">BV47+1</f>
-        <v>21</v>
-      </c>
-      <c r="BX47" s="1">
-        <f t="shared" ref="BX47" si="36">BW47+1</f>
-        <v>22</v>
-      </c>
-      <c r="BY47" s="1">
-        <f t="shared" ref="BY47" si="37">BX47+1</f>
-        <v>23</v>
-      </c>
-      <c r="BZ47" s="1">
-        <f t="shared" ref="BZ47" si="38">BY47+1</f>
-        <v>24</v>
-      </c>
-      <c r="CA47" s="1">
-        <f t="shared" ref="CA47" si="39">BZ47+1</f>
-        <v>25</v>
-      </c>
-      <c r="CB47" s="1">
-        <f t="shared" ref="CB47" si="40">CA47+1</f>
-        <v>26</v>
-      </c>
-      <c r="CC47" s="1">
-        <f t="shared" ref="CC47" si="41">CB47+1</f>
-        <v>27</v>
-      </c>
-      <c r="CD47" s="1">
-        <f t="shared" ref="CD47" si="42">CC47+1</f>
-        <v>28</v>
-      </c>
-      <c r="CE47" s="1">
-        <f t="shared" ref="CE47" si="43">CD47+1</f>
-        <v>29</v>
-      </c>
-      <c r="CF47" s="1">
-        <f t="shared" ref="CF47" si="44">CE47+1</f>
-        <v>30</v>
-      </c>
-      <c r="CG47" s="1">
-        <f t="shared" ref="CG47" si="45">CF47+1</f>
-        <v>31</v>
-      </c>
-      <c r="CH47" s="1">
-        <f t="shared" ref="CH47" si="46">CG47+1</f>
-        <v>32</v>
       </c>
       <c r="CN47" s="5"/>
       <c r="CO47" s="5"/>
@@ -11030,38 +9809,6 @@
       <c r="AR48" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="BC48" s="7"/>
-      <c r="BD48" s="7"/>
-      <c r="BE48" s="4"/>
-      <c r="BF48" s="4"/>
-      <c r="BG48" s="7"/>
-      <c r="BH48" s="7"/>
-      <c r="BI48" s="7"/>
-      <c r="BJ48" s="7"/>
-      <c r="BK48" s="4"/>
-      <c r="BL48" s="4"/>
-      <c r="BM48" s="4"/>
-      <c r="BN48" s="4"/>
-      <c r="BO48" s="7"/>
-      <c r="BP48" s="7"/>
-      <c r="BQ48" s="4"/>
-      <c r="BR48" s="4"/>
-      <c r="BS48" s="7"/>
-      <c r="BT48" s="7"/>
-      <c r="BU48" s="7"/>
-      <c r="BV48" s="7"/>
-      <c r="BW48" s="4"/>
-      <c r="BX48" s="4"/>
-      <c r="BY48" s="4"/>
-      <c r="BZ48" s="4"/>
-      <c r="CA48" s="7"/>
-      <c r="CB48" s="7"/>
-      <c r="CC48" s="4"/>
-      <c r="CD48" s="4"/>
-      <c r="CE48" s="7"/>
-      <c r="CF48" s="7"/>
-      <c r="CG48" s="7"/>
-      <c r="CH48" s="7"/>
       <c r="CN48" s="5"/>
       <c r="CO48" s="5"/>
       <c r="CP48" s="5" t="s">
@@ -11234,7 +9981,7 @@
     <row r="49" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F49" s="4"/>
       <c r="G49" s="1">
-        <f t="shared" ref="G49:G62" si="47">G48-1</f>
+        <f t="shared" ref="G49:G62" si="16">G48-1</f>
         <v>14</v>
       </c>
       <c r="H49" s="6" t="s">
@@ -11271,7 +10018,7 @@
       <c r="W49" s="5"/>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1">
-        <f t="shared" ref="AB49:AB62" si="48">AB48-1</f>
+        <f t="shared" ref="AB49:AB62" si="17">AB48-1</f>
         <v>14</v>
       </c>
       <c r="AC49" s="6" t="s">
@@ -11478,7 +10225,7 @@
     <row r="50" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F50" s="7"/>
       <c r="G50" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="H50" s="6" t="s">
@@ -11515,7 +10262,7 @@
       <c r="W50" s="6"/>
       <c r="AA50" s="7"/>
       <c r="AB50" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>13</v>
       </c>
       <c r="AC50" s="6" t="s">
@@ -11722,7 +10469,7 @@
     <row r="51" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F51" s="4"/>
       <c r="G51" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="H51" s="5"/>
@@ -11759,7 +10506,7 @@
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AC51" s="5"/>
@@ -11966,7 +10713,7 @@
     <row r="52" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F52" s="7"/>
       <c r="G52" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="H52" s="6"/>
@@ -12003,7 +10750,7 @@
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="AC52" s="5"/>
@@ -12210,7 +10957,7 @@
     <row r="53" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F53" s="4"/>
       <c r="G53" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="H53" s="6" t="s">
@@ -12247,7 +10994,7 @@
       <c r="W53" s="5"/>
       <c r="AA53" s="7"/>
       <c r="AB53" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>10</v>
       </c>
       <c r="AC53" s="6" t="s">
@@ -12454,7 +11201,7 @@
     <row r="54" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F54" s="7"/>
       <c r="G54" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="H54" s="6" t="s">
@@ -12491,7 +11238,7 @@
       <c r="W54" s="6"/>
       <c r="AA54" s="7"/>
       <c r="AB54" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="AC54" s="6" t="s">
@@ -12698,7 +11445,7 @@
     <row r="55" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F55" s="4"/>
       <c r="G55" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="H55" s="5"/>
@@ -12735,7 +11482,7 @@
       </c>
       <c r="AA55" s="4"/>
       <c r="AB55" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>8</v>
       </c>
       <c r="AC55" s="5"/>
@@ -12942,7 +11689,7 @@
     <row r="56" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F56" s="7"/>
       <c r="G56" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>7</v>
       </c>
       <c r="H56" s="6"/>
@@ -12979,7 +11726,7 @@
       </c>
       <c r="AA56" s="7"/>
       <c r="AB56" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>7</v>
       </c>
       <c r="AC56" s="6"/>
@@ -13186,7 +11933,7 @@
     <row r="57" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F57" s="4"/>
       <c r="G57" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="H57" s="6" t="s">
@@ -13223,7 +11970,7 @@
       <c r="W57" s="5"/>
       <c r="AA57" s="4"/>
       <c r="AB57" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="AC57" s="6" t="s">
@@ -13430,7 +12177,7 @@
     <row r="58" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F58" s="7"/>
       <c r="G58" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="H58" s="6" t="s">
@@ -13467,7 +12214,7 @@
       <c r="W58" s="6"/>
       <c r="AA58" s="4"/>
       <c r="AB58" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="AC58" s="6" t="s">
@@ -13674,7 +12421,7 @@
     <row r="59" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F59" s="4"/>
       <c r="G59" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="H59" s="5"/>
@@ -13711,7 +12458,7 @@
       </c>
       <c r="AA59" s="7"/>
       <c r="AB59" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="AC59" s="6"/>
@@ -13750,7 +12497,7 @@
     <row r="60" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F60" s="7"/>
       <c r="G60" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H60" s="6"/>
@@ -13787,7 +12534,7 @@
       </c>
       <c r="AA60" s="7"/>
       <c r="AB60" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="AC60" s="6"/>
@@ -13826,7 +12573,7 @@
     <row r="61" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F61" s="4"/>
       <c r="G61" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="H61" s="6" t="s">
@@ -13863,7 +12610,7 @@
       <c r="W61" s="5"/>
       <c r="AA61" s="4"/>
       <c r="AB61" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="AC61" s="6" t="s">
@@ -13902,7 +12649,7 @@
     <row r="62" spans="6:179" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F62" s="7"/>
       <c r="G62" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="H62" s="6" t="s">
@@ -13939,7 +12686,7 @@
       <c r="W62" s="6"/>
       <c r="AA62" s="7"/>
       <c r="AB62" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AC62" s="6" t="s">
@@ -13987,59 +12734,59 @@
         <v>2</v>
       </c>
       <c r="J63" s="1">
-        <f t="shared" ref="J63" si="49">I63+1</f>
+        <f t="shared" ref="J63" si="18">I63+1</f>
         <v>3</v>
       </c>
       <c r="K63" s="1">
-        <f t="shared" ref="K63" si="50">J63+1</f>
+        <f t="shared" ref="K63" si="19">J63+1</f>
         <v>4</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" ref="L63" si="51">K63+1</f>
+        <f t="shared" ref="L63" si="20">K63+1</f>
         <v>5</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" ref="M63" si="52">L63+1</f>
+        <f t="shared" ref="M63" si="21">L63+1</f>
         <v>6</v>
       </c>
       <c r="N63" s="1">
-        <f t="shared" ref="N63" si="53">M63+1</f>
+        <f t="shared" ref="N63" si="22">M63+1</f>
         <v>7</v>
       </c>
       <c r="O63" s="1">
-        <f t="shared" ref="O63" si="54">N63+1</f>
+        <f t="shared" ref="O63" si="23">N63+1</f>
         <v>8</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" ref="P63" si="55">O63+1</f>
+        <f t="shared" ref="P63" si="24">O63+1</f>
         <v>9</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" ref="Q63" si="56">P63+1</f>
+        <f t="shared" ref="Q63" si="25">P63+1</f>
         <v>10</v>
       </c>
       <c r="R63" s="1">
-        <f t="shared" ref="R63" si="57">Q63+1</f>
+        <f t="shared" ref="R63" si="26">Q63+1</f>
         <v>11</v>
       </c>
       <c r="S63" s="1">
-        <f t="shared" ref="S63" si="58">R63+1</f>
+        <f t="shared" ref="S63" si="27">R63+1</f>
         <v>12</v>
       </c>
       <c r="T63" s="1">
-        <f t="shared" ref="T63" si="59">S63+1</f>
+        <f t="shared" ref="T63" si="28">S63+1</f>
         <v>13</v>
       </c>
       <c r="U63" s="1">
-        <f t="shared" ref="U63" si="60">T63+1</f>
+        <f t="shared" ref="U63" si="29">T63+1</f>
         <v>14</v>
       </c>
       <c r="V63" s="1">
-        <f t="shared" ref="V63" si="61">U63+1</f>
+        <f t="shared" ref="V63" si="30">U63+1</f>
         <v>15</v>
       </c>
       <c r="W63" s="1">
-        <f t="shared" ref="W63" si="62">V63+1</f>
+        <f t="shared" ref="W63" si="31">V63+1</f>
         <v>16</v>
       </c>
       <c r="AB63" s="1" t="s">
@@ -14053,59 +12800,59 @@
         <v>2</v>
       </c>
       <c r="AE63" s="1">
-        <f t="shared" ref="AE63" si="63">AD63+1</f>
+        <f t="shared" ref="AE63" si="32">AD63+1</f>
         <v>3</v>
       </c>
       <c r="AF63" s="1">
-        <f t="shared" ref="AF63" si="64">AE63+1</f>
+        <f t="shared" ref="AF63" si="33">AE63+1</f>
         <v>4</v>
       </c>
       <c r="AG63" s="1">
-        <f t="shared" ref="AG63" si="65">AF63+1</f>
+        <f t="shared" ref="AG63" si="34">AF63+1</f>
         <v>5</v>
       </c>
       <c r="AH63" s="1">
-        <f t="shared" ref="AH63" si="66">AG63+1</f>
+        <f t="shared" ref="AH63" si="35">AG63+1</f>
         <v>6</v>
       </c>
       <c r="AI63" s="1">
-        <f t="shared" ref="AI63" si="67">AH63+1</f>
+        <f t="shared" ref="AI63" si="36">AH63+1</f>
         <v>7</v>
       </c>
       <c r="AJ63" s="1">
-        <f t="shared" ref="AJ63" si="68">AI63+1</f>
+        <f t="shared" ref="AJ63" si="37">AI63+1</f>
         <v>8</v>
       </c>
       <c r="AK63" s="1">
-        <f t="shared" ref="AK63" si="69">AJ63+1</f>
+        <f t="shared" ref="AK63" si="38">AJ63+1</f>
         <v>9</v>
       </c>
       <c r="AL63" s="1">
-        <f t="shared" ref="AL63" si="70">AK63+1</f>
+        <f t="shared" ref="AL63" si="39">AK63+1</f>
         <v>10</v>
       </c>
       <c r="AM63" s="1">
-        <f t="shared" ref="AM63" si="71">AL63+1</f>
+        <f t="shared" ref="AM63" si="40">AL63+1</f>
         <v>11</v>
       </c>
       <c r="AN63" s="1">
-        <f t="shared" ref="AN63" si="72">AM63+1</f>
+        <f t="shared" ref="AN63" si="41">AM63+1</f>
         <v>12</v>
       </c>
       <c r="AO63" s="1">
-        <f t="shared" ref="AO63" si="73">AN63+1</f>
+        <f t="shared" ref="AO63" si="42">AN63+1</f>
         <v>13</v>
       </c>
       <c r="AP63" s="1">
-        <f t="shared" ref="AP63" si="74">AO63+1</f>
+        <f t="shared" ref="AP63" si="43">AO63+1</f>
         <v>14</v>
       </c>
       <c r="AQ63" s="1">
-        <f t="shared" ref="AQ63" si="75">AP63+1</f>
+        <f t="shared" ref="AQ63" si="44">AP63+1</f>
         <v>15</v>
       </c>
       <c r="AR63" s="1">
-        <f t="shared" ref="AR63" si="76">AQ63+1</f>
+        <f t="shared" ref="AR63" si="45">AQ63+1</f>
         <v>16</v>
       </c>
     </row>
@@ -14143,7 +12890,7 @@
       <c r="AQ64" s="4"/>
       <c r="AR64" s="4"/>
     </row>
-    <row r="69" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P69" s="35"/>
       <c r="R69" s="34"/>
       <c r="S69" s="34"/>
@@ -14169,8 +12916,76 @@
       <c r="AC69" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK69" s="4"/>
+      <c r="AM69" s="1">
+        <v>32</v>
+      </c>
+      <c r="AN69" s="34"/>
+      <c r="AO69" s="34"/>
+      <c r="AP69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR69" s="34"/>
+      <c r="AS69" s="34"/>
+      <c r="AT69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV69" s="34"/>
+      <c r="AW69" s="34"/>
+      <c r="AX69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ69" s="34"/>
+      <c r="BA69" s="34"/>
+      <c r="BB69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ69" s="34"/>
+      <c r="BK69" s="34"/>
+      <c r="BL69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN69" s="34"/>
+      <c r="BO69" s="34"/>
+      <c r="BP69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR69" s="34"/>
+      <c r="BS69" s="34"/>
+      <c r="BT69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV69" s="34"/>
+      <c r="BW69" s="34"/>
+      <c r="BX69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY69" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P70" s="35"/>
       <c r="R70" s="34"/>
       <c r="S70" s="34" t="s">
@@ -14196,8 +13011,77 @@
         <v>1</v>
       </c>
       <c r="AC70" s="34"/>
-    </row>
-    <row r="71" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK70" s="4"/>
+      <c r="AM70" s="1">
+        <f>AM69-1</f>
+        <v>31</v>
+      </c>
+      <c r="AN70" s="34"/>
+      <c r="AO70" s="34"/>
+      <c r="AP70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR70" s="34"/>
+      <c r="AS70" s="34"/>
+      <c r="AT70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV70" s="34"/>
+      <c r="AW70" s="34"/>
+      <c r="AX70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ70" s="34"/>
+      <c r="BA70" s="34"/>
+      <c r="BB70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ70" s="34"/>
+      <c r="BK70" s="34"/>
+      <c r="BL70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN70" s="34"/>
+      <c r="BO70" s="34"/>
+      <c r="BP70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR70" s="34"/>
+      <c r="BS70" s="34"/>
+      <c r="BT70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV70" s="34"/>
+      <c r="BW70" s="34"/>
+      <c r="BX70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY70" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P71" s="36"/>
       <c r="R71" s="37" t="s">
         <v>1</v>
@@ -14223,8 +13107,77 @@
       </c>
       <c r="AB71" s="34"/>
       <c r="AC71" s="34"/>
-    </row>
-    <row r="72" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK71" s="7"/>
+      <c r="AM71" s="1">
+        <f t="shared" ref="AM71:AM83" si="46">AM70-1</f>
+        <v>30</v>
+      </c>
+      <c r="AN71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP71" s="34"/>
+      <c r="AQ71" s="34"/>
+      <c r="AR71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT71" s="34"/>
+      <c r="AU71" s="34"/>
+      <c r="AV71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX71" s="34"/>
+      <c r="AY71" s="34"/>
+      <c r="AZ71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB71" s="34"/>
+      <c r="BC71" s="34"/>
+      <c r="BJ71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL71" s="34"/>
+      <c r="BM71" s="34"/>
+      <c r="BN71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP71" s="34"/>
+      <c r="BQ71" s="34"/>
+      <c r="BR71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT71" s="34"/>
+      <c r="BU71" s="34"/>
+      <c r="BV71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX71" s="34"/>
+      <c r="BY71" s="34"/>
+    </row>
+    <row r="72" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P72" s="36"/>
       <c r="R72" s="37" t="s">
         <v>1</v>
@@ -14250,8 +13203,77 @@
       <c r="AC72" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK72" s="7"/>
+      <c r="AM72" s="1">
+        <f t="shared" si="46"/>
+        <v>29</v>
+      </c>
+      <c r="AN72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP72" s="34"/>
+      <c r="AQ72" s="34"/>
+      <c r="AR72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT72" s="34"/>
+      <c r="AU72" s="34"/>
+      <c r="AV72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX72" s="34"/>
+      <c r="AY72" s="34"/>
+      <c r="AZ72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB72" s="34"/>
+      <c r="BC72" s="34"/>
+      <c r="BJ72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL72" s="34"/>
+      <c r="BM72" s="34"/>
+      <c r="BN72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP72" s="34"/>
+      <c r="BQ72" s="34"/>
+      <c r="BR72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT72" s="34"/>
+      <c r="BU72" s="34"/>
+      <c r="BV72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX72" s="34"/>
+      <c r="BY72" s="34"/>
+    </row>
+    <row r="73" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P73" s="35"/>
       <c r="R73" s="34"/>
       <c r="S73" s="34"/>
@@ -14277,8 +13299,77 @@
       <c r="AC73" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK73" s="4"/>
+      <c r="AM73" s="1">
+        <f t="shared" si="46"/>
+        <v>28</v>
+      </c>
+      <c r="AN73" s="34"/>
+      <c r="AO73" s="34"/>
+      <c r="AP73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR73" s="34"/>
+      <c r="AS73" s="34"/>
+      <c r="AT73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV73" s="34"/>
+      <c r="AW73" s="34"/>
+      <c r="AX73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ73" s="34"/>
+      <c r="BA73" s="34"/>
+      <c r="BB73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ73" s="34"/>
+      <c r="BK73" s="34"/>
+      <c r="BL73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN73" s="34"/>
+      <c r="BO73" s="34"/>
+      <c r="BP73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR73" s="34"/>
+      <c r="BS73" s="34"/>
+      <c r="BT73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV73" s="34"/>
+      <c r="BW73" s="34"/>
+      <c r="BX73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY73" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P74" s="36"/>
       <c r="R74" s="34"/>
       <c r="S74" s="34" t="s">
@@ -14304,8 +13395,77 @@
         <v>1</v>
       </c>
       <c r="AC74" s="34"/>
-    </row>
-    <row r="75" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK74" s="4"/>
+      <c r="AM74" s="1">
+        <f t="shared" si="46"/>
+        <v>27</v>
+      </c>
+      <c r="AN74" s="34"/>
+      <c r="AO74" s="34"/>
+      <c r="AP74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR74" s="34"/>
+      <c r="AS74" s="34"/>
+      <c r="AT74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV74" s="34"/>
+      <c r="AW74" s="34"/>
+      <c r="AX74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ74" s="34"/>
+      <c r="BA74" s="34"/>
+      <c r="BB74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ74" s="34"/>
+      <c r="BK74" s="34"/>
+      <c r="BL74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN74" s="34"/>
+      <c r="BO74" s="34"/>
+      <c r="BP74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR74" s="34"/>
+      <c r="BS74" s="34"/>
+      <c r="BT74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV74" s="34"/>
+      <c r="BW74" s="34"/>
+      <c r="BX74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY74" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P75" s="35"/>
       <c r="R75" s="37" t="s">
         <v>1</v>
@@ -14331,8 +13491,77 @@
       </c>
       <c r="AB75" s="34"/>
       <c r="AC75" s="34"/>
-    </row>
-    <row r="76" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK75" s="7"/>
+      <c r="AM75" s="1">
+        <f t="shared" si="46"/>
+        <v>26</v>
+      </c>
+      <c r="AN75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP75" s="34"/>
+      <c r="AQ75" s="34"/>
+      <c r="AR75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT75" s="34"/>
+      <c r="AU75" s="34"/>
+      <c r="AV75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX75" s="34"/>
+      <c r="AY75" s="34"/>
+      <c r="AZ75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB75" s="34"/>
+      <c r="BC75" s="34"/>
+      <c r="BJ75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL75" s="34"/>
+      <c r="BM75" s="34"/>
+      <c r="BN75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP75" s="34"/>
+      <c r="BQ75" s="34"/>
+      <c r="BR75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT75" s="34"/>
+      <c r="BU75" s="34"/>
+      <c r="BV75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX75" s="34"/>
+      <c r="BY75" s="34"/>
+    </row>
+    <row r="76" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P76" s="35"/>
       <c r="R76" s="37" t="s">
         <v>1</v>
@@ -14358,8 +13587,77 @@
       <c r="AC76" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK76" s="7"/>
+      <c r="AM76" s="1">
+        <f t="shared" si="46"/>
+        <v>25</v>
+      </c>
+      <c r="AN76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP76" s="34"/>
+      <c r="AQ76" s="34"/>
+      <c r="AR76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT76" s="34"/>
+      <c r="AU76" s="34"/>
+      <c r="AV76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX76" s="34"/>
+      <c r="AY76" s="34"/>
+      <c r="AZ76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB76" s="34"/>
+      <c r="BC76" s="34"/>
+      <c r="BJ76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL76" s="34"/>
+      <c r="BM76" s="34"/>
+      <c r="BN76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP76" s="34"/>
+      <c r="BQ76" s="34"/>
+      <c r="BR76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT76" s="34"/>
+      <c r="BU76" s="34"/>
+      <c r="BV76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX76" s="34"/>
+      <c r="BY76" s="34"/>
+    </row>
+    <row r="77" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P77" s="36"/>
       <c r="R77" s="34"/>
       <c r="S77" s="34"/>
@@ -14385,8 +13683,77 @@
       <c r="AC77" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK77" s="4"/>
+      <c r="AM77" s="1">
+        <f t="shared" si="46"/>
+        <v>24</v>
+      </c>
+      <c r="AN77" s="34"/>
+      <c r="AO77" s="34"/>
+      <c r="AP77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR77" s="34"/>
+      <c r="AS77" s="34"/>
+      <c r="AT77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV77" s="34"/>
+      <c r="AW77" s="34"/>
+      <c r="AX77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ77" s="34"/>
+      <c r="BA77" s="34"/>
+      <c r="BB77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ77" s="34"/>
+      <c r="BK77" s="34"/>
+      <c r="BL77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN77" s="34"/>
+      <c r="BO77" s="34"/>
+      <c r="BP77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR77" s="34"/>
+      <c r="BS77" s="34"/>
+      <c r="BT77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV77" s="34"/>
+      <c r="BW77" s="34"/>
+      <c r="BX77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY77" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P78" s="36"/>
       <c r="R78" s="34"/>
       <c r="S78" s="34" t="s">
@@ -14412,8 +13779,77 @@
         <v>1</v>
       </c>
       <c r="AC78" s="34"/>
-    </row>
-    <row r="79" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK78" s="4"/>
+      <c r="AM78" s="1">
+        <f t="shared" si="46"/>
+        <v>23</v>
+      </c>
+      <c r="AN78" s="34"/>
+      <c r="AO78" s="34"/>
+      <c r="AP78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR78" s="34"/>
+      <c r="AS78" s="34"/>
+      <c r="AT78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV78" s="34"/>
+      <c r="AW78" s="34"/>
+      <c r="AX78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ78" s="34"/>
+      <c r="BA78" s="34"/>
+      <c r="BB78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ78" s="34"/>
+      <c r="BK78" s="34"/>
+      <c r="BL78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN78" s="34"/>
+      <c r="BO78" s="34"/>
+      <c r="BP78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR78" s="34"/>
+      <c r="BS78" s="34"/>
+      <c r="BT78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV78" s="34"/>
+      <c r="BW78" s="34"/>
+      <c r="BX78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY78" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P79" s="35"/>
       <c r="R79" s="37" t="s">
         <v>1</v>
@@ -14439,8 +13875,77 @@
       </c>
       <c r="AB79" s="34"/>
       <c r="AC79" s="34"/>
-    </row>
-    <row r="80" spans="16:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK79" s="7"/>
+      <c r="AM79" s="1">
+        <f t="shared" si="46"/>
+        <v>22</v>
+      </c>
+      <c r="AN79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP79" s="38"/>
+      <c r="AQ79" s="38"/>
+      <c r="AR79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT79" s="38"/>
+      <c r="AU79" s="38"/>
+      <c r="AV79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX79" s="38"/>
+      <c r="AY79" s="38"/>
+      <c r="AZ79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA79" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB79" s="38"/>
+      <c r="BC79" s="38"/>
+      <c r="BJ79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL79" s="34"/>
+      <c r="BM79" s="34"/>
+      <c r="BN79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP79" s="34"/>
+      <c r="BQ79" s="34"/>
+      <c r="BR79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT79" s="34"/>
+      <c r="BU79" s="34"/>
+      <c r="BV79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW79" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX79" s="34"/>
+      <c r="BY79" s="34"/>
+    </row>
+    <row r="80" spans="16:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P80" s="36"/>
       <c r="R80" s="37" t="s">
         <v>1</v>
@@ -14466,8 +13971,148 @@
       <c r="AC80" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="18:29" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK80" s="7"/>
+      <c r="AM80" s="1">
+        <f t="shared" si="46"/>
+        <v>21</v>
+      </c>
+      <c r="AN80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP80" s="38"/>
+      <c r="AQ80" s="38"/>
+      <c r="AR80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT80" s="38"/>
+      <c r="AU80" s="38"/>
+      <c r="AV80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX80" s="38"/>
+      <c r="AY80" s="38"/>
+      <c r="AZ80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA80" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB80" s="38"/>
+      <c r="BC80" s="38"/>
+      <c r="BJ80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL80" s="34"/>
+      <c r="BM80" s="34"/>
+      <c r="BN80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP80" s="34"/>
+      <c r="BQ80" s="34"/>
+      <c r="BR80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT80" s="34"/>
+      <c r="BU80" s="34"/>
+      <c r="BV80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX80" s="34"/>
+      <c r="BY80" s="34"/>
+    </row>
+    <row r="81" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK81" s="4"/>
+      <c r="AM81" s="1">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="AN81" s="5"/>
+      <c r="AO81" s="5"/>
+      <c r="AP81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR81" s="5"/>
+      <c r="AS81" s="5"/>
+      <c r="AT81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV81" s="5"/>
+      <c r="AW81" s="5"/>
+      <c r="AX81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ81" s="5"/>
+      <c r="BA81" s="5"/>
+      <c r="BB81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ81" s="34"/>
+      <c r="BK81" s="34"/>
+      <c r="BL81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN81" s="34"/>
+      <c r="BO81" s="34"/>
+      <c r="BP81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR81" s="34"/>
+      <c r="BS81" s="34"/>
+      <c r="BT81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV81" s="34"/>
+      <c r="BW81" s="34"/>
+      <c r="BX81" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY81" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R82" s="36"/>
       <c r="S82" s="35"/>
       <c r="T82" s="36"/>
@@ -14480,6 +14125,2741 @@
       <c r="AA82" s="36"/>
       <c r="AB82" s="35"/>
       <c r="AC82" s="35"/>
+      <c r="AK82" s="4"/>
+      <c r="AM82" s="1">
+        <f t="shared" si="46"/>
+        <v>19</v>
+      </c>
+      <c r="AN82" s="5"/>
+      <c r="AO82" s="5"/>
+      <c r="AP82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR82" s="5"/>
+      <c r="AS82" s="5"/>
+      <c r="AT82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV82" s="5"/>
+      <c r="AW82" s="5"/>
+      <c r="AX82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ82" s="5"/>
+      <c r="BA82" s="5"/>
+      <c r="BB82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ82" s="34"/>
+      <c r="BK82" s="34"/>
+      <c r="BL82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN82" s="34"/>
+      <c r="BO82" s="34"/>
+      <c r="BP82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR82" s="34"/>
+      <c r="BS82" s="34"/>
+      <c r="BT82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV82" s="34"/>
+      <c r="BW82" s="34"/>
+      <c r="BX82" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY82" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK83" s="7"/>
+      <c r="AM83" s="1">
+        <f t="shared" si="46"/>
+        <v>18</v>
+      </c>
+      <c r="AN83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP83" s="38"/>
+      <c r="AQ83" s="38"/>
+      <c r="AR83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT83" s="38"/>
+      <c r="AU83" s="38"/>
+      <c r="AV83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX83" s="38"/>
+      <c r="AY83" s="38"/>
+      <c r="AZ83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA83" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB83" s="38"/>
+      <c r="BC83" s="38"/>
+      <c r="BJ83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL83" s="34"/>
+      <c r="BM83" s="34"/>
+      <c r="BN83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP83" s="34"/>
+      <c r="BQ83" s="34"/>
+      <c r="BR83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT83" s="34"/>
+      <c r="BU83" s="34"/>
+      <c r="BV83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW83" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX83" s="34"/>
+      <c r="BY83" s="34"/>
+    </row>
+    <row r="84" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK84" s="7"/>
+      <c r="AM84" s="1">
+        <v>17</v>
+      </c>
+      <c r="AN84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP84" s="38"/>
+      <c r="AQ84" s="38"/>
+      <c r="AR84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT84" s="38"/>
+      <c r="AU84" s="38"/>
+      <c r="AV84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX84" s="38"/>
+      <c r="AY84" s="38"/>
+      <c r="AZ84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA84" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB84" s="38"/>
+      <c r="BC84" s="38"/>
+      <c r="BJ84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL84" s="34"/>
+      <c r="BM84" s="34"/>
+      <c r="BN84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP84" s="34"/>
+      <c r="BQ84" s="34"/>
+      <c r="BR84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT84" s="34"/>
+      <c r="BU84" s="34"/>
+      <c r="BV84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW84" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX84" s="34"/>
+      <c r="BY84" s="34"/>
+    </row>
+    <row r="85" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK85" s="4"/>
+      <c r="AM85" s="1">
+        <v>16</v>
+      </c>
+      <c r="AN85" s="5"/>
+      <c r="AO85" s="5"/>
+      <c r="AP85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR85" s="5"/>
+      <c r="AS85" s="5"/>
+      <c r="AT85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV85" s="5"/>
+      <c r="AW85" s="5"/>
+      <c r="AX85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ85" s="5"/>
+      <c r="BA85" s="5"/>
+      <c r="BB85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ85" s="34"/>
+      <c r="BK85" s="34"/>
+      <c r="BL85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN85" s="34"/>
+      <c r="BO85" s="34"/>
+      <c r="BP85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR85" s="34"/>
+      <c r="BS85" s="34"/>
+      <c r="BT85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV85" s="34"/>
+      <c r="BW85" s="34"/>
+      <c r="BX85" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY85" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK86" s="7"/>
+      <c r="AM86" s="1">
+        <f>AM85-1</f>
+        <v>15</v>
+      </c>
+      <c r="AN86" s="38"/>
+      <c r="AO86" s="38"/>
+      <c r="AP86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR86" s="38"/>
+      <c r="AS86" s="38"/>
+      <c r="AT86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV86" s="38"/>
+      <c r="AW86" s="38"/>
+      <c r="AX86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ86" s="38"/>
+      <c r="BA86" s="38"/>
+      <c r="BB86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ86" s="34"/>
+      <c r="BK86" s="34"/>
+      <c r="BL86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN86" s="34"/>
+      <c r="BO86" s="34"/>
+      <c r="BP86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR86" s="34"/>
+      <c r="BS86" s="34"/>
+      <c r="BT86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV86" s="34"/>
+      <c r="BW86" s="34"/>
+      <c r="BX86" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY86" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK87" s="4"/>
+      <c r="AM87" s="1">
+        <f t="shared" ref="AM87:AM100" si="47">AM86-1</f>
+        <v>14</v>
+      </c>
+      <c r="AN87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP87" s="5"/>
+      <c r="AQ87" s="5"/>
+      <c r="AR87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT87" s="5"/>
+      <c r="AU87" s="5"/>
+      <c r="AV87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX87" s="5"/>
+      <c r="AY87" s="5"/>
+      <c r="AZ87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA87" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB87" s="5"/>
+      <c r="BC87" s="5"/>
+      <c r="BJ87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL87" s="34"/>
+      <c r="BM87" s="34"/>
+      <c r="BN87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP87" s="34"/>
+      <c r="BQ87" s="34"/>
+      <c r="BR87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT87" s="34"/>
+      <c r="BU87" s="34"/>
+      <c r="BV87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW87" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX87" s="34"/>
+      <c r="BY87" s="34"/>
+    </row>
+    <row r="88" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK88" s="7"/>
+      <c r="AM88" s="1">
+        <f t="shared" si="47"/>
+        <v>13</v>
+      </c>
+      <c r="AN88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP88" s="38"/>
+      <c r="AQ88" s="38"/>
+      <c r="AR88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT88" s="38"/>
+      <c r="AU88" s="38"/>
+      <c r="AV88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX88" s="38"/>
+      <c r="AY88" s="38"/>
+      <c r="AZ88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA88" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB88" s="38"/>
+      <c r="BC88" s="38"/>
+      <c r="BJ88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL88" s="34"/>
+      <c r="BM88" s="34"/>
+      <c r="BN88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP88" s="34"/>
+      <c r="BQ88" s="34"/>
+      <c r="BR88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT88" s="34"/>
+      <c r="BU88" s="34"/>
+      <c r="BV88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW88" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX88" s="34"/>
+      <c r="BY88" s="34"/>
+    </row>
+    <row r="89" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK89" s="4"/>
+      <c r="AM89" s="1">
+        <f t="shared" si="47"/>
+        <v>12</v>
+      </c>
+      <c r="AN89" s="5"/>
+      <c r="AO89" s="5"/>
+      <c r="AP89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR89" s="5"/>
+      <c r="AS89" s="5"/>
+      <c r="AT89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV89" s="5"/>
+      <c r="AW89" s="5"/>
+      <c r="AX89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ89" s="5"/>
+      <c r="BA89" s="5"/>
+      <c r="BB89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ89" s="34"/>
+      <c r="BK89" s="34"/>
+      <c r="BL89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN89" s="34"/>
+      <c r="BO89" s="34"/>
+      <c r="BP89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR89" s="34"/>
+      <c r="BS89" s="34"/>
+      <c r="BT89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV89" s="34"/>
+      <c r="BW89" s="34"/>
+      <c r="BX89" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY89" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK90" s="7"/>
+      <c r="AM90" s="1">
+        <f t="shared" si="47"/>
+        <v>11</v>
+      </c>
+      <c r="AN90" s="38"/>
+      <c r="AO90" s="38"/>
+      <c r="AP90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR90" s="38"/>
+      <c r="AS90" s="38"/>
+      <c r="AT90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV90" s="38"/>
+      <c r="AW90" s="38"/>
+      <c r="AX90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ90" s="38"/>
+      <c r="BA90" s="38"/>
+      <c r="BB90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ90" s="34"/>
+      <c r="BK90" s="34"/>
+      <c r="BL90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN90" s="34"/>
+      <c r="BO90" s="34"/>
+      <c r="BP90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR90" s="34"/>
+      <c r="BS90" s="34"/>
+      <c r="BT90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV90" s="34"/>
+      <c r="BW90" s="34"/>
+      <c r="BX90" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY90" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK91" s="4"/>
+      <c r="AM91" s="1">
+        <f t="shared" si="47"/>
+        <v>10</v>
+      </c>
+      <c r="AN91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP91" s="5"/>
+      <c r="AQ91" s="5"/>
+      <c r="AR91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT91" s="5"/>
+      <c r="AU91" s="5"/>
+      <c r="AV91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX91" s="5"/>
+      <c r="AY91" s="5"/>
+      <c r="AZ91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA91" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB91" s="5"/>
+      <c r="BC91" s="5"/>
+      <c r="BJ91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL91" s="34"/>
+      <c r="BM91" s="34"/>
+      <c r="BN91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP91" s="34"/>
+      <c r="BQ91" s="34"/>
+      <c r="BR91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT91" s="34"/>
+      <c r="BU91" s="34"/>
+      <c r="BV91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW91" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX91" s="34"/>
+      <c r="BY91" s="34"/>
+    </row>
+    <row r="92" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK92" s="7"/>
+      <c r="AM92" s="1">
+        <f t="shared" si="47"/>
+        <v>9</v>
+      </c>
+      <c r="AN92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP92" s="38"/>
+      <c r="AQ92" s="38"/>
+      <c r="AR92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT92" s="38"/>
+      <c r="AU92" s="38"/>
+      <c r="AV92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX92" s="38"/>
+      <c r="AY92" s="38"/>
+      <c r="AZ92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA92" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB92" s="38"/>
+      <c r="BC92" s="38"/>
+      <c r="BJ92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL92" s="34"/>
+      <c r="BM92" s="34"/>
+      <c r="BN92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP92" s="34"/>
+      <c r="BQ92" s="34"/>
+      <c r="BR92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT92" s="34"/>
+      <c r="BU92" s="34"/>
+      <c r="BV92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW92" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX92" s="34"/>
+      <c r="BY92" s="34"/>
+    </row>
+    <row r="93" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK93" s="4"/>
+      <c r="AM93" s="1">
+        <f t="shared" si="47"/>
+        <v>8</v>
+      </c>
+      <c r="AN93" s="5"/>
+      <c r="AO93" s="5"/>
+      <c r="AP93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR93" s="5"/>
+      <c r="AS93" s="5"/>
+      <c r="AT93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV93" s="5"/>
+      <c r="AW93" s="5"/>
+      <c r="AX93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ93" s="5"/>
+      <c r="BA93" s="5"/>
+      <c r="BB93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ93" s="34"/>
+      <c r="BK93" s="34"/>
+      <c r="BL93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN93" s="34"/>
+      <c r="BO93" s="34"/>
+      <c r="BP93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR93" s="34"/>
+      <c r="BS93" s="34"/>
+      <c r="BT93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV93" s="34"/>
+      <c r="BW93" s="34"/>
+      <c r="BX93" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY93" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK94" s="7"/>
+      <c r="AM94" s="1">
+        <f t="shared" si="47"/>
+        <v>7</v>
+      </c>
+      <c r="AN94" s="38"/>
+      <c r="AO94" s="38"/>
+      <c r="AP94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR94" s="38"/>
+      <c r="AS94" s="38"/>
+      <c r="AT94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV94" s="38"/>
+      <c r="AW94" s="38"/>
+      <c r="AX94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ94" s="38"/>
+      <c r="BA94" s="38"/>
+      <c r="BB94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ94" s="34"/>
+      <c r="BK94" s="34"/>
+      <c r="BL94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN94" s="34"/>
+      <c r="BO94" s="34"/>
+      <c r="BP94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR94" s="34"/>
+      <c r="BS94" s="34"/>
+      <c r="BT94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV94" s="34"/>
+      <c r="BW94" s="34"/>
+      <c r="BX94" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY94" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK95" s="4"/>
+      <c r="AM95" s="1">
+        <f t="shared" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="AN95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP95" s="5"/>
+      <c r="AQ95" s="5"/>
+      <c r="AR95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT95" s="5"/>
+      <c r="AU95" s="5"/>
+      <c r="AV95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX95" s="5"/>
+      <c r="AY95" s="5"/>
+      <c r="AZ95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA95" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB95" s="5"/>
+      <c r="BC95" s="5"/>
+      <c r="BJ95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL95" s="34"/>
+      <c r="BM95" s="34"/>
+      <c r="BN95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP95" s="34"/>
+      <c r="BQ95" s="34"/>
+      <c r="BR95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT95" s="34"/>
+      <c r="BU95" s="34"/>
+      <c r="BV95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW95" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX95" s="34"/>
+      <c r="BY95" s="34"/>
+    </row>
+    <row r="96" spans="18:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK96" s="7"/>
+      <c r="AM96" s="1">
+        <f t="shared" si="47"/>
+        <v>5</v>
+      </c>
+      <c r="AN96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP96" s="38"/>
+      <c r="AQ96" s="38"/>
+      <c r="AR96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT96" s="38"/>
+      <c r="AU96" s="38"/>
+      <c r="AV96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX96" s="38"/>
+      <c r="AY96" s="38"/>
+      <c r="AZ96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA96" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB96" s="38"/>
+      <c r="BC96" s="38"/>
+      <c r="BJ96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL96" s="34"/>
+      <c r="BM96" s="34"/>
+      <c r="BN96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP96" s="34"/>
+      <c r="BQ96" s="34"/>
+      <c r="BR96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT96" s="34"/>
+      <c r="BU96" s="34"/>
+      <c r="BV96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW96" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX96" s="34"/>
+      <c r="BY96" s="34"/>
+    </row>
+    <row r="97" spans="37:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK97" s="4"/>
+      <c r="AM97" s="1">
+        <f t="shared" si="47"/>
+        <v>4</v>
+      </c>
+      <c r="AN97" s="5"/>
+      <c r="AO97" s="5"/>
+      <c r="AP97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR97" s="5"/>
+      <c r="AS97" s="5"/>
+      <c r="AT97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV97" s="5"/>
+      <c r="AW97" s="5"/>
+      <c r="AX97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ97" s="5"/>
+      <c r="BA97" s="5"/>
+      <c r="BB97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ97" s="34"/>
+      <c r="BK97" s="34"/>
+      <c r="BL97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN97" s="34"/>
+      <c r="BO97" s="34"/>
+      <c r="BP97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR97" s="34"/>
+      <c r="BS97" s="34"/>
+      <c r="BT97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV97" s="34"/>
+      <c r="BW97" s="34"/>
+      <c r="BX97" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY97" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="37:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK98" s="7"/>
+      <c r="AM98" s="1">
+        <f t="shared" si="47"/>
+        <v>3</v>
+      </c>
+      <c r="AN98" s="38"/>
+      <c r="AO98" s="38"/>
+      <c r="AP98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR98" s="38"/>
+      <c r="AS98" s="38"/>
+      <c r="AT98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV98" s="38"/>
+      <c r="AW98" s="38"/>
+      <c r="AX98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ98" s="38"/>
+      <c r="BA98" s="38"/>
+      <c r="BB98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ98" s="34"/>
+      <c r="BK98" s="34"/>
+      <c r="BL98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN98" s="34"/>
+      <c r="BO98" s="34"/>
+      <c r="BP98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR98" s="34"/>
+      <c r="BS98" s="34"/>
+      <c r="BT98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV98" s="34"/>
+      <c r="BW98" s="34"/>
+      <c r="BX98" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY98" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="37:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK99" s="4"/>
+      <c r="AM99" s="1">
+        <f t="shared" si="47"/>
+        <v>2</v>
+      </c>
+      <c r="AN99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP99" s="5"/>
+      <c r="AQ99" s="5"/>
+      <c r="AR99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT99" s="5"/>
+      <c r="AU99" s="5"/>
+      <c r="AV99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX99" s="5"/>
+      <c r="AY99" s="5"/>
+      <c r="AZ99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA99" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB99" s="5"/>
+      <c r="BC99" s="5"/>
+      <c r="BJ99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL99" s="34"/>
+      <c r="BM99" s="34"/>
+      <c r="BN99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP99" s="34"/>
+      <c r="BQ99" s="34"/>
+      <c r="BR99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT99" s="34"/>
+      <c r="BU99" s="34"/>
+      <c r="BV99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW99" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX99" s="34"/>
+      <c r="BY99" s="34"/>
+    </row>
+    <row r="100" spans="37:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AK100" s="7"/>
+      <c r="AM100" s="1">
+        <f t="shared" si="47"/>
+        <v>1</v>
+      </c>
+      <c r="AN100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP100" s="38"/>
+      <c r="AQ100" s="38"/>
+      <c r="AR100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT100" s="38"/>
+      <c r="AU100" s="38"/>
+      <c r="AV100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX100" s="38"/>
+      <c r="AY100" s="38"/>
+      <c r="AZ100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB100" s="38"/>
+      <c r="BC100" s="38"/>
+      <c r="BH100" s="39"/>
+      <c r="BJ100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL100" s="38"/>
+      <c r="BM100" s="38"/>
+      <c r="BN100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP100" s="38"/>
+      <c r="BQ100" s="38"/>
+      <c r="BR100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT100" s="38"/>
+      <c r="BU100" s="38"/>
+      <c r="BV100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW100" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX100" s="38"/>
+      <c r="BY100" s="38"/>
+    </row>
+    <row r="101" spans="37:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AM101" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO101" s="1">
+        <f>AN101+1</f>
+        <v>2</v>
+      </c>
+      <c r="AP101" s="1">
+        <f t="shared" ref="AP101" si="48">AO101+1</f>
+        <v>3</v>
+      </c>
+      <c r="AQ101" s="1">
+        <f t="shared" ref="AQ101" si="49">AP101+1</f>
+        <v>4</v>
+      </c>
+      <c r="AR101" s="1">
+        <f t="shared" ref="AR101" si="50">AQ101+1</f>
+        <v>5</v>
+      </c>
+      <c r="AS101" s="1">
+        <f t="shared" ref="AS101" si="51">AR101+1</f>
+        <v>6</v>
+      </c>
+      <c r="AT101" s="1">
+        <f t="shared" ref="AT101" si="52">AS101+1</f>
+        <v>7</v>
+      </c>
+      <c r="AU101" s="1">
+        <f t="shared" ref="AU101" si="53">AT101+1</f>
+        <v>8</v>
+      </c>
+      <c r="AV101" s="1">
+        <f t="shared" ref="AV101" si="54">AU101+1</f>
+        <v>9</v>
+      </c>
+      <c r="AW101" s="1">
+        <f t="shared" ref="AW101" si="55">AV101+1</f>
+        <v>10</v>
+      </c>
+      <c r="AX101" s="1">
+        <f t="shared" ref="AX101" si="56">AW101+1</f>
+        <v>11</v>
+      </c>
+      <c r="AY101" s="1">
+        <f t="shared" ref="AY101" si="57">AX101+1</f>
+        <v>12</v>
+      </c>
+      <c r="AZ101" s="1">
+        <f t="shared" ref="AZ101" si="58">AY101+1</f>
+        <v>13</v>
+      </c>
+      <c r="BA101" s="1">
+        <f t="shared" ref="BA101" si="59">AZ101+1</f>
+        <v>14</v>
+      </c>
+      <c r="BB101" s="1">
+        <f t="shared" ref="BB101" si="60">BA101+1</f>
+        <v>15</v>
+      </c>
+      <c r="BC101" s="1">
+        <f t="shared" ref="BC101" si="61">BB101+1</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="37:77" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AN102" s="7"/>
+      <c r="AO102" s="7"/>
+      <c r="AP102" s="4"/>
+      <c r="AQ102" s="4"/>
+      <c r="AR102" s="7"/>
+      <c r="AS102" s="7"/>
+      <c r="AT102" s="4"/>
+      <c r="AU102" s="4"/>
+      <c r="AV102" s="7"/>
+      <c r="AW102" s="7"/>
+      <c r="AX102" s="4"/>
+      <c r="AY102" s="4"/>
+      <c r="AZ102" s="7"/>
+      <c r="BA102" s="7"/>
+      <c r="BB102" s="4"/>
+      <c r="BC102" s="4"/>
+      <c r="BJ102" s="39"/>
+      <c r="BK102" s="39"/>
+    </row>
+    <row r="117" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F117" s="4"/>
+      <c r="G117" s="1">
+        <v>16</v>
+      </c>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L117" s="5"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P117" s="5"/>
+      <c r="Q117" s="5"/>
+      <c r="R117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T117" s="5"/>
+      <c r="U117" s="5"/>
+      <c r="V117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X117" s="5"/>
+      <c r="Y117" s="5"/>
+      <c r="Z117" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA117" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB117" s="5"/>
+      <c r="AC117" s="5"/>
+      <c r="AD117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF117" s="5"/>
+      <c r="AG117" s="5"/>
+      <c r="AH117" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI117" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ117" s="5"/>
+      <c r="AK117" s="5"/>
+      <c r="AL117" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM117" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F118" s="4"/>
+      <c r="G118" s="1">
+        <f>G117-1</f>
+        <v>15</v>
+      </c>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L118" s="5"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P118" s="5"/>
+      <c r="Q118" s="5"/>
+      <c r="R118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T118" s="5"/>
+      <c r="U118" s="5"/>
+      <c r="V118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X118" s="5"/>
+      <c r="Y118" s="5"/>
+      <c r="Z118" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA118" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB118" s="5"/>
+      <c r="AC118" s="5"/>
+      <c r="AD118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF118" s="5"/>
+      <c r="AG118" s="5"/>
+      <c r="AH118" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI118" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ118" s="5"/>
+      <c r="AK118" s="5"/>
+      <c r="AL118" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM118" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F119" s="7"/>
+      <c r="G119" s="1">
+        <f t="shared" ref="G119:G132" si="62">G118-1</f>
+        <v>14</v>
+      </c>
+      <c r="H119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J119" s="38"/>
+      <c r="K119" s="38"/>
+      <c r="L119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N119" s="38"/>
+      <c r="O119" s="38"/>
+      <c r="P119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R119" s="38"/>
+      <c r="S119" s="38"/>
+      <c r="T119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V119" s="38"/>
+      <c r="W119" s="38"/>
+      <c r="X119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y119" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z119" s="38"/>
+      <c r="AA119" s="38"/>
+      <c r="AB119" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC119" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD119" s="38"/>
+      <c r="AE119" s="38"/>
+      <c r="AF119" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG119" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH119" s="38"/>
+      <c r="AI119" s="38"/>
+      <c r="AJ119" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK119" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL119" s="38"/>
+      <c r="AM119" s="38"/>
+    </row>
+    <row r="120" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F120" s="7"/>
+      <c r="G120" s="1">
+        <f t="shared" si="62"/>
+        <v>13</v>
+      </c>
+      <c r="H120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J120" s="38"/>
+      <c r="K120" s="38"/>
+      <c r="L120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N120" s="38"/>
+      <c r="O120" s="38"/>
+      <c r="P120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R120" s="38"/>
+      <c r="S120" s="38"/>
+      <c r="T120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V120" s="38"/>
+      <c r="W120" s="38"/>
+      <c r="X120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y120" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z120" s="38"/>
+      <c r="AA120" s="38"/>
+      <c r="AB120" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC120" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD120" s="38"/>
+      <c r="AE120" s="38"/>
+      <c r="AF120" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG120" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH120" s="38"/>
+      <c r="AI120" s="38"/>
+      <c r="AJ120" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK120" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL120" s="38"/>
+      <c r="AM120" s="38"/>
+    </row>
+    <row r="121" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F121" s="4"/>
+      <c r="G121" s="1">
+        <f t="shared" si="62"/>
+        <v>12</v>
+      </c>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P121" s="5"/>
+      <c r="Q121" s="5"/>
+      <c r="R121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T121" s="5"/>
+      <c r="U121" s="5"/>
+      <c r="V121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5"/>
+      <c r="Z121" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA121" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="5"/>
+      <c r="AC121" s="5"/>
+      <c r="AD121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE121" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF121" s="5"/>
+      <c r="AG121" s="5"/>
+      <c r="AH121" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI121" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ121" s="5"/>
+      <c r="AK121" s="5"/>
+      <c r="AL121" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM121" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F122" s="4"/>
+      <c r="G122" s="1">
+        <f t="shared" si="62"/>
+        <v>11</v>
+      </c>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L122" s="5"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P122" s="5"/>
+      <c r="Q122" s="5"/>
+      <c r="R122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T122" s="5"/>
+      <c r="U122" s="5"/>
+      <c r="V122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X122" s="5"/>
+      <c r="Y122" s="5"/>
+      <c r="Z122" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA122" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB122" s="5"/>
+      <c r="AC122" s="5"/>
+      <c r="AD122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE122" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF122" s="5"/>
+      <c r="AG122" s="5"/>
+      <c r="AH122" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI122" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ122" s="5"/>
+      <c r="AK122" s="5"/>
+      <c r="AL122" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM122" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F123" s="7"/>
+      <c r="G123" s="1">
+        <f t="shared" si="62"/>
+        <v>10</v>
+      </c>
+      <c r="H123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J123" s="38"/>
+      <c r="K123" s="38"/>
+      <c r="L123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N123" s="38"/>
+      <c r="O123" s="38"/>
+      <c r="P123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R123" s="38"/>
+      <c r="S123" s="38"/>
+      <c r="T123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V123" s="38"/>
+      <c r="W123" s="38"/>
+      <c r="X123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y123" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z123" s="38"/>
+      <c r="AA123" s="38"/>
+      <c r="AB123" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC123" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD123" s="38"/>
+      <c r="AE123" s="38"/>
+      <c r="AF123" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG123" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH123" s="38"/>
+      <c r="AI123" s="38"/>
+      <c r="AJ123" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK123" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL123" s="38"/>
+      <c r="AM123" s="38"/>
+    </row>
+    <row r="124" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F124" s="7"/>
+      <c r="G124" s="1">
+        <f t="shared" si="62"/>
+        <v>9</v>
+      </c>
+      <c r="H124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J124" s="38"/>
+      <c r="K124" s="38"/>
+      <c r="L124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N124" s="38"/>
+      <c r="O124" s="38"/>
+      <c r="P124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R124" s="38"/>
+      <c r="S124" s="38"/>
+      <c r="T124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V124" s="38"/>
+      <c r="W124" s="38"/>
+      <c r="X124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y124" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z124" s="38"/>
+      <c r="AA124" s="38"/>
+      <c r="AB124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD124" s="38"/>
+      <c r="AE124" s="38"/>
+      <c r="AF124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH124" s="38"/>
+      <c r="AI124" s="38"/>
+      <c r="AJ124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL124" s="38"/>
+      <c r="AM124" s="38"/>
+    </row>
+    <row r="125" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F125" s="4"/>
+      <c r="G125" s="1">
+        <f t="shared" si="62"/>
+        <v>8</v>
+      </c>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L125" s="5"/>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P125" s="5"/>
+      <c r="Q125" s="5"/>
+      <c r="R125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T125" s="5"/>
+      <c r="U125" s="5"/>
+      <c r="V125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X125" s="5"/>
+      <c r="Y125" s="5"/>
+      <c r="Z125" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA125" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB125" s="5"/>
+      <c r="AC125" s="5"/>
+      <c r="AD125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE125" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF125" s="5"/>
+      <c r="AG125" s="5"/>
+      <c r="AH125" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI125" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ125" s="5"/>
+      <c r="AK125" s="5"/>
+      <c r="AL125" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM125" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F126" s="4"/>
+      <c r="G126" s="1">
+        <f t="shared" si="62"/>
+        <v>7</v>
+      </c>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L126" s="5"/>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P126" s="5"/>
+      <c r="Q126" s="5"/>
+      <c r="R126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T126" s="5"/>
+      <c r="U126" s="5"/>
+      <c r="V126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X126" s="5"/>
+      <c r="Y126" s="5"/>
+      <c r="Z126" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA126" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB126" s="5"/>
+      <c r="AC126" s="5"/>
+      <c r="AD126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE126" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF126" s="5"/>
+      <c r="AG126" s="5"/>
+      <c r="AH126" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI126" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ126" s="5"/>
+      <c r="AK126" s="5"/>
+      <c r="AL126" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM126" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F127" s="7"/>
+      <c r="G127" s="1">
+        <f t="shared" si="62"/>
+        <v>6</v>
+      </c>
+      <c r="H127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J127" s="38"/>
+      <c r="K127" s="38"/>
+      <c r="L127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N127" s="38"/>
+      <c r="O127" s="38"/>
+      <c r="P127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R127" s="38"/>
+      <c r="S127" s="38"/>
+      <c r="T127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V127" s="38"/>
+      <c r="W127" s="38"/>
+      <c r="X127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y127" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z127" s="38"/>
+      <c r="AA127" s="38"/>
+      <c r="AB127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD127" s="38"/>
+      <c r="AE127" s="38"/>
+      <c r="AF127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH127" s="38"/>
+      <c r="AI127" s="38"/>
+      <c r="AJ127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL127" s="38"/>
+      <c r="AM127" s="38"/>
+    </row>
+    <row r="128" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F128" s="7"/>
+      <c r="G128" s="1">
+        <f t="shared" si="62"/>
+        <v>5</v>
+      </c>
+      <c r="H128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J128" s="38"/>
+      <c r="K128" s="38"/>
+      <c r="L128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N128" s="38"/>
+      <c r="O128" s="38"/>
+      <c r="P128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R128" s="38"/>
+      <c r="S128" s="38"/>
+      <c r="T128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V128" s="38"/>
+      <c r="W128" s="38"/>
+      <c r="X128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y128" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z128" s="38"/>
+      <c r="AA128" s="38"/>
+      <c r="AB128" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC128" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD128" s="38"/>
+      <c r="AE128" s="38"/>
+      <c r="AF128" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG128" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH128" s="38"/>
+      <c r="AI128" s="38"/>
+      <c r="AJ128" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK128" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL128" s="38"/>
+      <c r="AM128" s="38"/>
+    </row>
+    <row r="129" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F129" s="4"/>
+      <c r="G129" s="1">
+        <f t="shared" si="62"/>
+        <v>4</v>
+      </c>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L129" s="5"/>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P129" s="5"/>
+      <c r="Q129" s="5"/>
+      <c r="R129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T129" s="5"/>
+      <c r="U129" s="5"/>
+      <c r="V129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X129" s="5"/>
+      <c r="Y129" s="5"/>
+      <c r="Z129" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA129" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB129" s="5"/>
+      <c r="AC129" s="5"/>
+      <c r="AD129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE129" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF129" s="5"/>
+      <c r="AG129" s="5"/>
+      <c r="AH129" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI129" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ129" s="5"/>
+      <c r="AK129" s="5"/>
+      <c r="AL129" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM129" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F130" s="4"/>
+      <c r="G130" s="1">
+        <f t="shared" si="62"/>
+        <v>3</v>
+      </c>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L130" s="5"/>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P130" s="5"/>
+      <c r="Q130" s="5"/>
+      <c r="R130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T130" s="5"/>
+      <c r="U130" s="5"/>
+      <c r="V130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="W130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X130" s="5"/>
+      <c r="Y130" s="5"/>
+      <c r="Z130" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA130" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="5"/>
+      <c r="AC130" s="5"/>
+      <c r="AD130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF130" s="5"/>
+      <c r="AG130" s="5"/>
+      <c r="AH130" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI130" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ130" s="5"/>
+      <c r="AK130" s="5"/>
+      <c r="AL130" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM130" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F131" s="7"/>
+      <c r="G131" s="1">
+        <f t="shared" si="62"/>
+        <v>2</v>
+      </c>
+      <c r="H131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J131" s="38"/>
+      <c r="K131" s="38"/>
+      <c r="L131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N131" s="38"/>
+      <c r="O131" s="38"/>
+      <c r="P131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R131" s="38"/>
+      <c r="S131" s="38"/>
+      <c r="T131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V131" s="38"/>
+      <c r="W131" s="38"/>
+      <c r="X131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y131" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z131" s="38"/>
+      <c r="AA131" s="38"/>
+      <c r="AB131" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC131" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD131" s="38"/>
+      <c r="AE131" s="38"/>
+      <c r="AF131" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG131" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH131" s="38"/>
+      <c r="AI131" s="38"/>
+      <c r="AJ131" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK131" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL131" s="38"/>
+      <c r="AM131" s="38"/>
+    </row>
+    <row r="132" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F132" s="7"/>
+      <c r="G132" s="1">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="H132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J132" s="38"/>
+      <c r="K132" s="38"/>
+      <c r="L132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N132" s="38"/>
+      <c r="O132" s="38"/>
+      <c r="P132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R132" s="38"/>
+      <c r="S132" s="38"/>
+      <c r="T132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="U132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="V132" s="38"/>
+      <c r="W132" s="38"/>
+      <c r="X132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y132" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z132" s="38"/>
+      <c r="AA132" s="38"/>
+      <c r="AB132" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC132" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD132" s="38"/>
+      <c r="AE132" s="38"/>
+      <c r="AF132" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG132" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH132" s="38"/>
+      <c r="AI132" s="38"/>
+      <c r="AJ132" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK132" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL132" s="38"/>
+      <c r="AM132" s="38"/>
+    </row>
+    <row r="133" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G133" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>1</v>
+      </c>
+      <c r="I133" s="1">
+        <f>H133+1</f>
+        <v>2</v>
+      </c>
+      <c r="J133" s="1">
+        <f t="shared" ref="J133" si="63">I133+1</f>
+        <v>3</v>
+      </c>
+      <c r="K133" s="1">
+        <f t="shared" ref="K133" si="64">J133+1</f>
+        <v>4</v>
+      </c>
+      <c r="L133" s="1">
+        <f t="shared" ref="L133" si="65">K133+1</f>
+        <v>5</v>
+      </c>
+      <c r="M133" s="1">
+        <f t="shared" ref="M133" si="66">L133+1</f>
+        <v>6</v>
+      </c>
+      <c r="N133" s="1">
+        <f t="shared" ref="N133" si="67">M133+1</f>
+        <v>7</v>
+      </c>
+      <c r="O133" s="1">
+        <f t="shared" ref="O133" si="68">N133+1</f>
+        <v>8</v>
+      </c>
+      <c r="P133" s="1">
+        <f t="shared" ref="P133" si="69">O133+1</f>
+        <v>9</v>
+      </c>
+      <c r="Q133" s="1">
+        <f t="shared" ref="Q133" si="70">P133+1</f>
+        <v>10</v>
+      </c>
+      <c r="R133" s="1">
+        <f t="shared" ref="R133" si="71">Q133+1</f>
+        <v>11</v>
+      </c>
+      <c r="S133" s="1">
+        <f t="shared" ref="S133" si="72">R133+1</f>
+        <v>12</v>
+      </c>
+      <c r="T133" s="1">
+        <f t="shared" ref="T133" si="73">S133+1</f>
+        <v>13</v>
+      </c>
+      <c r="U133" s="1">
+        <f t="shared" ref="U133" si="74">T133+1</f>
+        <v>14</v>
+      </c>
+      <c r="V133" s="1">
+        <f t="shared" ref="V133" si="75">U133+1</f>
+        <v>15</v>
+      </c>
+      <c r="W133" s="1">
+        <f t="shared" ref="W133" si="76">V133+1</f>
+        <v>16</v>
+      </c>
+      <c r="X133" s="1">
+        <f t="shared" ref="X133" si="77">W133+1</f>
+        <v>17</v>
+      </c>
+      <c r="Y133" s="1">
+        <f t="shared" ref="Y133" si="78">X133+1</f>
+        <v>18</v>
+      </c>
+      <c r="Z133" s="1">
+        <f t="shared" ref="Z133" si="79">Y133+1</f>
+        <v>19</v>
+      </c>
+      <c r="AA133" s="1">
+        <f t="shared" ref="AA133" si="80">Z133+1</f>
+        <v>20</v>
+      </c>
+      <c r="AB133" s="1">
+        <f t="shared" ref="AB133" si="81">AA133+1</f>
+        <v>21</v>
+      </c>
+      <c r="AC133" s="1">
+        <f t="shared" ref="AC133" si="82">AB133+1</f>
+        <v>22</v>
+      </c>
+      <c r="AD133" s="1">
+        <f t="shared" ref="AD133" si="83">AC133+1</f>
+        <v>23</v>
+      </c>
+      <c r="AE133" s="1">
+        <f t="shared" ref="AE133" si="84">AD133+1</f>
+        <v>24</v>
+      </c>
+      <c r="AF133" s="1">
+        <f t="shared" ref="AF133" si="85">AE133+1</f>
+        <v>25</v>
+      </c>
+      <c r="AG133" s="1">
+        <f t="shared" ref="AG133" si="86">AF133+1</f>
+        <v>26</v>
+      </c>
+      <c r="AH133" s="1">
+        <f t="shared" ref="AH133" si="87">AG133+1</f>
+        <v>27</v>
+      </c>
+      <c r="AI133" s="1">
+        <f t="shared" ref="AI133" si="88">AH133+1</f>
+        <v>28</v>
+      </c>
+      <c r="AJ133" s="1">
+        <f t="shared" ref="AJ133" si="89">AI133+1</f>
+        <v>29</v>
+      </c>
+      <c r="AK133" s="1">
+        <f t="shared" ref="AK133" si="90">AJ133+1</f>
+        <v>30</v>
+      </c>
+      <c r="AL133" s="1">
+        <f t="shared" ref="AL133" si="91">AK133+1</f>
+        <v>31</v>
+      </c>
+      <c r="AM133" s="1">
+        <f t="shared" ref="AM133" si="92">AL133+1</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="6:39" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+      <c r="L134" s="7"/>
+      <c r="M134" s="7"/>
+      <c r="N134" s="4"/>
+      <c r="O134" s="4"/>
+      <c r="P134" s="7"/>
+      <c r="Q134" s="7"/>
+      <c r="R134" s="4"/>
+      <c r="S134" s="4"/>
+      <c r="T134" s="7"/>
+      <c r="U134" s="7"/>
+      <c r="V134" s="4"/>
+      <c r="W134" s="4"/>
+      <c r="X134" s="7"/>
+      <c r="Y134" s="7"/>
+      <c r="Z134" s="7"/>
+      <c r="AA134" s="7"/>
+      <c r="AB134" s="4"/>
+      <c r="AC134" s="4"/>
+      <c r="AD134" s="4"/>
+      <c r="AE134" s="4"/>
+      <c r="AF134" s="7"/>
+      <c r="AG134" s="7"/>
+      <c r="AH134" s="7"/>
+      <c r="AI134" s="7"/>
+      <c r="AJ134" s="4"/>
+      <c r="AK134" s="4"/>
+      <c r="AL134" s="4"/>
+      <c r="AM134" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
